--- a/app/templates_excel/nigredo/n7_asteroids_en.xlsx
+++ b/app/templates_excel/nigredo/n7_asteroids_en.xlsx
@@ -1300,10 +1300,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A window at an open grave.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A bridge being built across a gorge.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1560,10 +1556,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Chinese woman nusing a baby with a message.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>One hand slightly flexed with a very prominent thumb.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2532,10 +2524,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A gigatic tent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A master instructing his pupil.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2605,6 +2593,18 @@
   </si>
   <si>
     <t>A professor peering over his glasses.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A gigantic tent.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese woman nursing a baby with a message.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A widow at an open grave.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3715,25 +3715,25 @@
     </row>
     <row r="39" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3773,7 +3773,7 @@
         <v>31</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>407</v>
+        <v>733</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3781,7 +3781,7 @@
         <v>32</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3789,7 +3789,7 @@
         <v>33</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3797,7 +3797,7 @@
         <v>34</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3805,7 +3805,7 @@
         <v>35</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3813,7 +3813,7 @@
         <v>36</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3821,7 +3821,7 @@
         <v>37</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3829,7 +3829,7 @@
         <v>38</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3837,7 +3837,7 @@
         <v>39</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3845,7 +3845,7 @@
         <v>40</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3853,7 +3853,7 @@
         <v>41</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3861,7 +3861,7 @@
         <v>42</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3869,7 +3869,7 @@
         <v>43</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3877,7 +3877,7 @@
         <v>44</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3885,7 +3885,7 @@
         <v>45</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3893,7 +3893,7 @@
         <v>46</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3901,7 +3901,7 @@
         <v>47</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3909,7 +3909,7 @@
         <v>48</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3917,7 +3917,7 @@
         <v>49</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.4">
@@ -3925,7 +3925,7 @@
         <v>50</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.4">
@@ -3933,7 +3933,7 @@
         <v>51</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.4">
@@ -3941,7 +3941,7 @@
         <v>52</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.4">
@@ -3949,7 +3949,7 @@
         <v>53</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.4">
@@ -3957,7 +3957,7 @@
         <v>54</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.4">
@@ -3965,7 +3965,7 @@
         <v>55</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.4">
@@ -3973,30 +3973,30 @@
         <v>56</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="70" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B70" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.4">
@@ -4004,7 +4004,7 @@
         <v>365</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.4">
@@ -4012,7 +4012,7 @@
         <v>366</v>
       </c>
       <c r="I72" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.4">
@@ -4020,7 +4020,7 @@
         <v>57</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.4">
@@ -4028,7 +4028,7 @@
         <v>58</v>
       </c>
       <c r="I74" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.4">
@@ -4036,7 +4036,7 @@
         <v>59</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.4">
@@ -4044,7 +4044,7 @@
         <v>60</v>
       </c>
       <c r="I76" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.4">
@@ -4052,7 +4052,7 @@
         <v>61</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.4">
@@ -4060,7 +4060,7 @@
         <v>62</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.4">
@@ -4068,7 +4068,7 @@
         <v>63</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.4">
@@ -4076,7 +4076,7 @@
         <v>64</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.4">
@@ -4084,7 +4084,7 @@
         <v>65</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.4">
@@ -4092,7 +4092,7 @@
         <v>66</v>
       </c>
       <c r="I82" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.4">
@@ -4100,7 +4100,7 @@
         <v>67</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.4">
@@ -4108,7 +4108,7 @@
         <v>68</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.4">
@@ -4116,7 +4116,7 @@
         <v>69</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.4">
@@ -4124,7 +4124,7 @@
         <v>70</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.4">
@@ -4132,7 +4132,7 @@
         <v>71</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.4">
@@ -4140,7 +4140,7 @@
         <v>72</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.4">
@@ -4148,7 +4148,7 @@
         <v>73</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.4">
@@ -4156,7 +4156,7 @@
         <v>74</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.4">
@@ -4164,7 +4164,7 @@
         <v>75</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.4">
@@ -4172,7 +4172,7 @@
         <v>76</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.4">
@@ -4180,7 +4180,7 @@
         <v>77</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.4">
@@ -4188,7 +4188,7 @@
         <v>78</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.4">
@@ -4196,7 +4196,7 @@
         <v>79</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.4">
@@ -4204,7 +4204,7 @@
         <v>80</v>
       </c>
       <c r="I96" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.4">
@@ -4212,7 +4212,7 @@
         <v>81</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.4">
@@ -4220,7 +4220,7 @@
         <v>82</v>
       </c>
       <c r="I98" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.4">
@@ -4228,7 +4228,7 @@
         <v>83</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.4">
@@ -4236,30 +4236,30 @@
         <v>84</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="101" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B101" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.4">
@@ -4267,7 +4267,7 @@
         <v>367</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.4">
@@ -4275,7 +4275,7 @@
         <v>85</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.4">
@@ -4283,7 +4283,7 @@
         <v>86</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.4">
@@ -4291,7 +4291,7 @@
         <v>87</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.4">
@@ -4299,7 +4299,7 @@
         <v>88</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.4">
@@ -4307,7 +4307,7 @@
         <v>89</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.4">
@@ -4315,7 +4315,7 @@
         <v>90</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.4">
@@ -4323,7 +4323,7 @@
         <v>91</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.4">
@@ -4331,7 +4331,7 @@
         <v>92</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.4">
@@ -4339,7 +4339,7 @@
         <v>93</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.4">
@@ -4347,7 +4347,7 @@
         <v>94</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.4">
@@ -4355,7 +4355,7 @@
         <v>95</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>472</v>
+        <v>732</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>96</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.4">
@@ -4371,7 +4371,7 @@
         <v>97</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.4">
@@ -4379,7 +4379,7 @@
         <v>98</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.4">
@@ -4387,7 +4387,7 @@
         <v>99</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.4">
@@ -4395,7 +4395,7 @@
         <v>100</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.4">
@@ -4403,7 +4403,7 @@
         <v>101</v>
       </c>
       <c r="I119" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.4">
@@ -4411,7 +4411,7 @@
         <v>102</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>103</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.4">
@@ -4427,7 +4427,7 @@
         <v>104</v>
       </c>
       <c r="I122" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.4">
@@ -4435,7 +4435,7 @@
         <v>105</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.4">
@@ -4443,7 +4443,7 @@
         <v>106</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.4">
@@ -4451,7 +4451,7 @@
         <v>107</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.4">
@@ -4459,7 +4459,7 @@
         <v>108</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.4">
@@ -4467,7 +4467,7 @@
         <v>109</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>110</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.4">
@@ -4483,7 +4483,7 @@
         <v>111</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.4">
@@ -4491,7 +4491,7 @@
         <v>112</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.4">
@@ -4499,30 +4499,30 @@
         <v>113</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="132" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.4">
@@ -4530,7 +4530,7 @@
         <v>368</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.4">
@@ -4538,7 +4538,7 @@
         <v>114</v>
       </c>
       <c r="I134" s="7" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.4">
@@ -4546,7 +4546,7 @@
         <v>115</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.4">
@@ -4554,7 +4554,7 @@
         <v>116</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.4">
@@ -4562,7 +4562,7 @@
         <v>117</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.4">
@@ -4570,7 +4570,7 @@
         <v>118</v>
       </c>
       <c r="I138" s="7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.4">
@@ -4578,7 +4578,7 @@
         <v>119</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.4">
@@ -4586,7 +4586,7 @@
         <v>120</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.4">
@@ -4594,7 +4594,7 @@
         <v>121</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.4">
@@ -4602,7 +4602,7 @@
         <v>122</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.4">
@@ -4610,7 +4610,7 @@
         <v>123</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.4">
@@ -4618,7 +4618,7 @@
         <v>124</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.4">
@@ -4626,7 +4626,7 @@
         <v>125</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.4">
@@ -4634,7 +4634,7 @@
         <v>126</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.4">
@@ -4642,7 +4642,7 @@
         <v>127</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.4">
@@ -4650,7 +4650,7 @@
         <v>128</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.4">
@@ -4658,7 +4658,7 @@
         <v>129</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.4">
@@ -4666,7 +4666,7 @@
         <v>130</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.4">
@@ -4674,7 +4674,7 @@
         <v>131</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.4">
@@ -4682,7 +4682,7 @@
         <v>132</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.4">
@@ -4690,7 +4690,7 @@
         <v>133</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.4">
@@ -4698,7 +4698,7 @@
         <v>134</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.4">
@@ -4706,7 +4706,7 @@
         <v>135</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.4">
@@ -4714,7 +4714,7 @@
         <v>136</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.4">
@@ -4722,7 +4722,7 @@
         <v>137</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.4">
@@ -4730,7 +4730,7 @@
         <v>138</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.4">
@@ -4738,7 +4738,7 @@
         <v>139</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.4">
@@ -4746,7 +4746,7 @@
         <v>140</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.4">
@@ -4754,7 +4754,7 @@
         <v>141</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.4">
@@ -4762,30 +4762,30 @@
         <v>142</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="163" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B163" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.4">
@@ -4793,7 +4793,7 @@
         <v>369</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.4">
@@ -4801,7 +4801,7 @@
         <v>370</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.4">
@@ -4809,7 +4809,7 @@
         <v>143</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.4">
@@ -4817,7 +4817,7 @@
         <v>144</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>145</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.4">
@@ -4833,7 +4833,7 @@
         <v>146</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.4">
@@ -4841,7 +4841,7 @@
         <v>147</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.4">
@@ -4849,7 +4849,7 @@
         <v>148</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.4">
@@ -4857,7 +4857,7 @@
         <v>149</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.4">
@@ -4865,7 +4865,7 @@
         <v>150</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.4">
@@ -4873,7 +4873,7 @@
         <v>151</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>152</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.4">
@@ -4889,7 +4889,7 @@
         <v>153</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.4">
@@ -4897,7 +4897,7 @@
         <v>154</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.4">
@@ -4905,7 +4905,7 @@
         <v>155</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.4">
@@ -4913,7 +4913,7 @@
         <v>156</v>
       </c>
       <c r="I179" s="7" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.4">
@@ -4921,7 +4921,7 @@
         <v>157</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.4">
@@ -4929,7 +4929,7 @@
         <v>158</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>159</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.4">
@@ -4945,7 +4945,7 @@
         <v>160</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.4">
@@ -4953,7 +4953,7 @@
         <v>161</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.4">
@@ -4961,7 +4961,7 @@
         <v>162</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.4">
@@ -4969,7 +4969,7 @@
         <v>163</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.4">
@@ -4977,7 +4977,7 @@
         <v>164</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.4">
@@ -4985,7 +4985,7 @@
         <v>165</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>166</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.4">
@@ -5001,7 +5001,7 @@
         <v>167</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.4">
@@ -5009,7 +5009,7 @@
         <v>168</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.4">
@@ -5017,7 +5017,7 @@
         <v>169</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.4">
@@ -5025,30 +5025,30 @@
         <v>170</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="194" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B194" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="H194" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.4">
@@ -5056,7 +5056,7 @@
         <v>371</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.4">
@@ -5064,7 +5064,7 @@
         <v>171</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.4">
@@ -5072,7 +5072,7 @@
         <v>172</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.4">
@@ -5080,7 +5080,7 @@
         <v>173</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.4">
@@ -5088,7 +5088,7 @@
         <v>174</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.4">
@@ -5096,7 +5096,7 @@
         <v>175</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.4">
@@ -5104,7 +5104,7 @@
         <v>176</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.4">
@@ -5112,7 +5112,7 @@
         <v>177</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.4">
@@ -5120,7 +5120,7 @@
         <v>178</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.4">
@@ -5128,7 +5128,7 @@
         <v>179</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.4">
@@ -5136,7 +5136,7 @@
         <v>180</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.4">
@@ -5144,7 +5144,7 @@
         <v>181</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.4">
@@ -5152,7 +5152,7 @@
         <v>182</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.4">
@@ -5160,7 +5160,7 @@
         <v>183</v>
       </c>
       <c r="I208" s="7" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.4">
@@ -5168,7 +5168,7 @@
         <v>184</v>
       </c>
       <c r="I209" s="7" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.4">
@@ -5176,7 +5176,7 @@
         <v>185</v>
       </c>
       <c r="I210" s="7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.4">
@@ -5184,7 +5184,7 @@
         <v>186</v>
       </c>
       <c r="I211" s="7" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.4">
@@ -5192,7 +5192,7 @@
         <v>187</v>
       </c>
       <c r="I212" s="7" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.4">
@@ -5200,7 +5200,7 @@
         <v>188</v>
       </c>
       <c r="I213" s="7" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.4">
@@ -5208,7 +5208,7 @@
         <v>189</v>
       </c>
       <c r="I214" s="7" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.4">
@@ -5216,7 +5216,7 @@
         <v>190</v>
       </c>
       <c r="I215" s="7" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.4">
@@ -5224,7 +5224,7 @@
         <v>191</v>
       </c>
       <c r="I216" s="7" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.4">
@@ -5232,7 +5232,7 @@
         <v>192</v>
       </c>
       <c r="I217" s="7" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.4">
@@ -5240,7 +5240,7 @@
         <v>193</v>
       </c>
       <c r="I218" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.4">
@@ -5248,7 +5248,7 @@
         <v>194</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.4">
@@ -5256,7 +5256,7 @@
         <v>195</v>
       </c>
       <c r="I220" s="7" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.4">
@@ -5264,7 +5264,7 @@
         <v>196</v>
       </c>
       <c r="I221" s="7" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.4">
@@ -5272,7 +5272,7 @@
         <v>197</v>
       </c>
       <c r="I222" s="7" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.4">
@@ -5280,7 +5280,7 @@
         <v>198</v>
       </c>
       <c r="I223" s="7" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.4">
@@ -5288,30 +5288,30 @@
         <v>199</v>
       </c>
       <c r="I224" s="7" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="225" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B225" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E225" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F225" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G225" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.4">
@@ -5319,7 +5319,7 @@
         <v>372</v>
       </c>
       <c r="I226" s="7" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.4">
@@ -5327,7 +5327,7 @@
         <v>200</v>
       </c>
       <c r="I227" s="7" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.4">
@@ -5335,7 +5335,7 @@
         <v>201</v>
       </c>
       <c r="I228" s="7" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.4">
@@ -5343,7 +5343,7 @@
         <v>202</v>
       </c>
       <c r="I229" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.4">
@@ -5351,7 +5351,7 @@
         <v>203</v>
       </c>
       <c r="I230" s="7" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.4">
@@ -5359,7 +5359,7 @@
         <v>204</v>
       </c>
       <c r="I231" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.4">
@@ -5367,7 +5367,7 @@
         <v>205</v>
       </c>
       <c r="I232" s="7" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.4">
@@ -5375,7 +5375,7 @@
         <v>206</v>
       </c>
       <c r="I233" s="7" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.4">
@@ -5383,7 +5383,7 @@
         <v>207</v>
       </c>
       <c r="I234" s="7" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.4">
@@ -5391,7 +5391,7 @@
         <v>208</v>
       </c>
       <c r="I235" s="7" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.4">
@@ -5399,7 +5399,7 @@
         <v>209</v>
       </c>
       <c r="I236" s="7" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.4">
@@ -5407,7 +5407,7 @@
         <v>210</v>
       </c>
       <c r="I237" s="7" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.4">
@@ -5415,7 +5415,7 @@
         <v>211</v>
       </c>
       <c r="I238" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.4">
@@ -5423,7 +5423,7 @@
         <v>212</v>
       </c>
       <c r="I239" s="7" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.4">
@@ -5431,7 +5431,7 @@
         <v>213</v>
       </c>
       <c r="I240" s="7" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.4">
@@ -5439,7 +5439,7 @@
         <v>214</v>
       </c>
       <c r="I241" s="7" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.4">
@@ -5447,7 +5447,7 @@
         <v>215</v>
       </c>
       <c r="I242" s="7" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.4">
@@ -5455,7 +5455,7 @@
         <v>216</v>
       </c>
       <c r="I243" s="7" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.4">
@@ -5463,7 +5463,7 @@
         <v>217</v>
       </c>
       <c r="I244" s="7" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.4">
@@ -5471,7 +5471,7 @@
         <v>218</v>
       </c>
       <c r="I245" s="7" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.4">
@@ -5479,7 +5479,7 @@
         <v>219</v>
       </c>
       <c r="I246" s="7" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.4">
@@ -5487,7 +5487,7 @@
         <v>220</v>
       </c>
       <c r="I247" s="7" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.4">
@@ -5495,7 +5495,7 @@
         <v>221</v>
       </c>
       <c r="I248" s="7" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.4">
@@ -5503,7 +5503,7 @@
         <v>222</v>
       </c>
       <c r="I249" s="7" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.4">
@@ -5511,7 +5511,7 @@
         <v>223</v>
       </c>
       <c r="I250" s="7" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.4">
@@ -5519,7 +5519,7 @@
         <v>224</v>
       </c>
       <c r="I251" s="7" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.4">
@@ -5527,7 +5527,7 @@
         <v>225</v>
       </c>
       <c r="I252" s="7" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.4">
@@ -5535,7 +5535,7 @@
         <v>226</v>
       </c>
       <c r="I253" s="7" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.4">
@@ -5543,7 +5543,7 @@
         <v>227</v>
       </c>
       <c r="I254" s="7" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.4">
@@ -5551,30 +5551,30 @@
         <v>228</v>
       </c>
       <c r="I255" s="7" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="256" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B256" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C256" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E256" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F256" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G256" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="H256" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.4">
@@ -5582,7 +5582,7 @@
         <v>373</v>
       </c>
       <c r="I257" s="7" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.4">
@@ -5590,7 +5590,7 @@
         <v>229</v>
       </c>
       <c r="I258" s="7" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.4">
@@ -5598,7 +5598,7 @@
         <v>230</v>
       </c>
       <c r="I259" s="7" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.4">
@@ -5606,7 +5606,7 @@
         <v>231</v>
       </c>
       <c r="I260" s="7" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.4">
@@ -5614,7 +5614,7 @@
         <v>232</v>
       </c>
       <c r="I261" s="7" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.4">
@@ -5622,7 +5622,7 @@
         <v>233</v>
       </c>
       <c r="I262" s="7" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.4">
@@ -5630,7 +5630,7 @@
         <v>234</v>
       </c>
       <c r="I263" s="7" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.4">
@@ -5638,7 +5638,7 @@
         <v>235</v>
       </c>
       <c r="I264" s="7" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.4">
@@ -5646,7 +5646,7 @@
         <v>236</v>
       </c>
       <c r="I265" s="7" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.4">
@@ -5654,7 +5654,7 @@
         <v>0</v>
       </c>
       <c r="I266" s="7" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.4">
@@ -5662,7 +5662,7 @@
         <v>237</v>
       </c>
       <c r="I267" s="7" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.4">
@@ -5670,7 +5670,7 @@
         <v>238</v>
       </c>
       <c r="I268" s="7" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.4">
@@ -5678,7 +5678,7 @@
         <v>239</v>
       </c>
       <c r="I269" s="7" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.4">
@@ -5686,7 +5686,7 @@
         <v>240</v>
       </c>
       <c r="I270" s="7" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.4">
@@ -5694,7 +5694,7 @@
         <v>241</v>
       </c>
       <c r="I271" s="7" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.4">
@@ -5702,7 +5702,7 @@
         <v>242</v>
       </c>
       <c r="I272" s="7" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.4">
@@ -5710,7 +5710,7 @@
         <v>243</v>
       </c>
       <c r="I273" s="7" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.4">
@@ -5718,7 +5718,7 @@
         <v>244</v>
       </c>
       <c r="I274" s="7" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.4">
@@ -5726,7 +5726,7 @@
         <v>245</v>
       </c>
       <c r="I275" s="7" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.4">
@@ -5734,7 +5734,7 @@
         <v>246</v>
       </c>
       <c r="I276" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.4">
@@ -5742,7 +5742,7 @@
         <v>247</v>
       </c>
       <c r="I277" s="7" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.4">
@@ -5750,7 +5750,7 @@
         <v>248</v>
       </c>
       <c r="I278" s="7" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.4">
@@ -5758,7 +5758,7 @@
         <v>249</v>
       </c>
       <c r="I279" s="7" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.4">
@@ -5766,7 +5766,7 @@
         <v>250</v>
       </c>
       <c r="I280" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.4">
@@ -5774,7 +5774,7 @@
         <v>251</v>
       </c>
       <c r="I281" s="7" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.4">
@@ -5782,7 +5782,7 @@
         <v>252</v>
       </c>
       <c r="I282" s="7" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.4">
@@ -5790,7 +5790,7 @@
         <v>253</v>
       </c>
       <c r="I283" s="7" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.4">
@@ -5798,7 +5798,7 @@
         <v>254</v>
       </c>
       <c r="I284" s="7" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.4">
@@ -5806,7 +5806,7 @@
         <v>255</v>
       </c>
       <c r="I285" s="7" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.4">
@@ -5814,30 +5814,30 @@
         <v>256</v>
       </c>
       <c r="I286" s="7" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="287" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B287" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F287" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G287" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="H287" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.4">
@@ -5845,7 +5845,7 @@
         <v>374</v>
       </c>
       <c r="I288" s="7" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.4">
@@ -5853,7 +5853,7 @@
         <v>257</v>
       </c>
       <c r="I289" s="7" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.4">
@@ -5861,7 +5861,7 @@
         <v>258</v>
       </c>
       <c r="I290" s="7" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.4">
@@ -5869,7 +5869,7 @@
         <v>259</v>
       </c>
       <c r="I291" s="7" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.4">
@@ -5877,7 +5877,7 @@
         <v>260</v>
       </c>
       <c r="I292" s="7" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.4">
@@ -5885,7 +5885,7 @@
         <v>261</v>
       </c>
       <c r="I293" s="7" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.4">
@@ -5893,7 +5893,7 @@
         <v>262</v>
       </c>
       <c r="I294" s="7" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.4">
@@ -5901,7 +5901,7 @@
         <v>263</v>
       </c>
       <c r="I295" s="7" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.4">
@@ -5909,7 +5909,7 @@
         <v>264</v>
       </c>
       <c r="I296" s="7" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.4">
@@ -5917,7 +5917,7 @@
         <v>265</v>
       </c>
       <c r="I297" s="7" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.4">
@@ -5925,7 +5925,7 @@
         <v>266</v>
       </c>
       <c r="I298" s="7" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.4">
@@ -5933,7 +5933,7 @@
         <v>267</v>
       </c>
       <c r="I299" s="7" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.4">
@@ -5941,7 +5941,7 @@
         <v>268</v>
       </c>
       <c r="I300" s="7" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.4">
@@ -5949,7 +5949,7 @@
         <v>269</v>
       </c>
       <c r="I301" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.4">
@@ -5957,7 +5957,7 @@
         <v>270</v>
       </c>
       <c r="I302" s="7" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.4">
@@ -5965,7 +5965,7 @@
         <v>271</v>
       </c>
       <c r="I303" s="7" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.4">
@@ -5973,7 +5973,7 @@
         <v>272</v>
       </c>
       <c r="I304" s="7" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.4">
@@ -5981,7 +5981,7 @@
         <v>273</v>
       </c>
       <c r="I305" s="7" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.4">
@@ -5989,7 +5989,7 @@
         <v>274</v>
       </c>
       <c r="I306" s="7" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.4">
@@ -5997,7 +5997,7 @@
         <v>275</v>
       </c>
       <c r="I307" s="7" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.4">
@@ -6005,7 +6005,7 @@
         <v>276</v>
       </c>
       <c r="I308" s="7" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.4">
@@ -6013,7 +6013,7 @@
         <v>277</v>
       </c>
       <c r="I309" s="7" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.4">
@@ -6021,7 +6021,7 @@
         <v>278</v>
       </c>
       <c r="I310" s="7" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.4">
@@ -6029,7 +6029,7 @@
         <v>279</v>
       </c>
       <c r="I311" s="7" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.4">
@@ -6037,7 +6037,7 @@
         <v>280</v>
       </c>
       <c r="I312" s="7" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.4">
@@ -6045,7 +6045,7 @@
         <v>281</v>
       </c>
       <c r="I313" s="7" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.4">
@@ -6053,7 +6053,7 @@
         <v>282</v>
       </c>
       <c r="I314" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.4">
@@ -6061,7 +6061,7 @@
         <v>283</v>
       </c>
       <c r="I315" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.4">
@@ -6069,7 +6069,7 @@
         <v>284</v>
       </c>
       <c r="I316" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.4">
@@ -6077,30 +6077,30 @@
         <v>285</v>
       </c>
       <c r="I317" s="7" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="318" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B318" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C318" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D318" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E318" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F318" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G318" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="H318" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.4">
@@ -6108,7 +6108,7 @@
         <v>375</v>
       </c>
       <c r="I319" s="7" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.4">
@@ -6116,7 +6116,7 @@
         <v>286</v>
       </c>
       <c r="I320" s="7" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.4">
@@ -6124,7 +6124,7 @@
         <v>287</v>
       </c>
       <c r="I321" s="7" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.4">
@@ -6132,7 +6132,7 @@
         <v>288</v>
       </c>
       <c r="I322" s="7" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.4">
@@ -6140,7 +6140,7 @@
         <v>289</v>
       </c>
       <c r="I323" s="7" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.4">
@@ -6148,7 +6148,7 @@
         <v>290</v>
       </c>
       <c r="I324" s="7" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.4">
@@ -6156,7 +6156,7 @@
         <v>291</v>
       </c>
       <c r="I325" s="7" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.4">
@@ -6164,7 +6164,7 @@
         <v>292</v>
       </c>
       <c r="I326" s="7" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.4">
@@ -6172,7 +6172,7 @@
         <v>293</v>
       </c>
       <c r="I327" s="7" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.4">
@@ -6180,7 +6180,7 @@
         <v>294</v>
       </c>
       <c r="I328" s="7" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.4">
@@ -6188,7 +6188,7 @@
         <v>295</v>
       </c>
       <c r="I329" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.4">
@@ -6196,7 +6196,7 @@
         <v>296</v>
       </c>
       <c r="I330" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.4">
@@ -6204,7 +6204,7 @@
         <v>297</v>
       </c>
       <c r="I331" s="7" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.4">
@@ -6212,7 +6212,7 @@
         <v>298</v>
       </c>
       <c r="I332" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.4">
@@ -6220,7 +6220,7 @@
         <v>299</v>
       </c>
       <c r="I333" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.4">
@@ -6228,7 +6228,7 @@
         <v>300</v>
       </c>
       <c r="I334" s="7" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.4">
@@ -6236,7 +6236,7 @@
         <v>301</v>
       </c>
       <c r="I335" s="7" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.4">
@@ -6244,7 +6244,7 @@
         <v>302</v>
       </c>
       <c r="I336" s="7" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.4">
@@ -6252,7 +6252,7 @@
         <v>303</v>
       </c>
       <c r="I337" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.4">
@@ -6260,7 +6260,7 @@
         <v>304</v>
       </c>
       <c r="I338" s="7" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.4">
@@ -6268,7 +6268,7 @@
         <v>305</v>
       </c>
       <c r="I339" s="7" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.4">
@@ -6276,7 +6276,7 @@
         <v>306</v>
       </c>
       <c r="I340" s="7" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.4">
@@ -6284,7 +6284,7 @@
         <v>307</v>
       </c>
       <c r="I341" s="7" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.4">
@@ -6292,7 +6292,7 @@
         <v>308</v>
       </c>
       <c r="I342" s="7" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.4">
@@ -6300,7 +6300,7 @@
         <v>309</v>
       </c>
       <c r="I343" s="7" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.4">
@@ -6308,7 +6308,7 @@
         <v>310</v>
       </c>
       <c r="I344" s="7" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.4">
@@ -6316,7 +6316,7 @@
         <v>311</v>
       </c>
       <c r="I345" s="7" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.4">
@@ -6324,7 +6324,7 @@
         <v>312</v>
       </c>
       <c r="I346" s="7" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.4">
@@ -6332,7 +6332,7 @@
         <v>313</v>
       </c>
       <c r="I347" s="7" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.4">
@@ -6340,30 +6340,30 @@
         <v>314</v>
       </c>
       <c r="I348" s="7" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="349" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B349" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C349" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D349" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E349" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F349" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G349" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="H349" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.4">
@@ -6371,7 +6371,7 @@
         <v>376</v>
       </c>
       <c r="I350" s="7" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.4">
@@ -6379,7 +6379,7 @@
         <v>315</v>
       </c>
       <c r="I351" s="7" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.4">
@@ -6387,7 +6387,7 @@
         <v>316</v>
       </c>
       <c r="I352" s="7" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.4">
@@ -6395,7 +6395,7 @@
         <v>317</v>
       </c>
       <c r="I353" s="7" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.4">
@@ -6403,7 +6403,7 @@
         <v>318</v>
       </c>
       <c r="I354" s="7" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.4">
@@ -6411,7 +6411,7 @@
         <v>319</v>
       </c>
       <c r="I355" s="7" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.4">
@@ -6419,7 +6419,7 @@
         <v>320</v>
       </c>
       <c r="I356" s="7" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.4">
@@ -6427,7 +6427,7 @@
         <v>321</v>
       </c>
       <c r="I357" s="7" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.4">
@@ -6435,7 +6435,7 @@
         <v>322</v>
       </c>
       <c r="I358" s="7" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.4">
@@ -6443,7 +6443,7 @@
         <v>323</v>
       </c>
       <c r="I359" s="7" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.4">
@@ -6451,7 +6451,7 @@
         <v>324</v>
       </c>
       <c r="I360" s="7" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.4">
@@ -6459,7 +6459,7 @@
         <v>325</v>
       </c>
       <c r="I361" s="7" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.4">
@@ -6467,7 +6467,7 @@
         <v>326</v>
       </c>
       <c r="I362" s="7" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.4">
@@ -6475,7 +6475,7 @@
         <v>327</v>
       </c>
       <c r="I363" s="7" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.4">
@@ -6483,7 +6483,7 @@
         <v>328</v>
       </c>
       <c r="I364" s="7" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.4">
@@ -6491,7 +6491,7 @@
         <v>329</v>
       </c>
       <c r="I365" s="7" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.4">
@@ -6499,7 +6499,7 @@
         <v>330</v>
       </c>
       <c r="I366" s="7" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.4">
@@ -6507,7 +6507,7 @@
         <v>331</v>
       </c>
       <c r="I367" s="7" t="s">
-        <v>715</v>
+        <v>731</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.4">
@@ -6515,7 +6515,7 @@
         <v>332</v>
       </c>
       <c r="I368" s="7" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.4">
@@ -6523,7 +6523,7 @@
         <v>333</v>
       </c>
       <c r="I369" s="7" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.4">
@@ -6531,7 +6531,7 @@
         <v>334</v>
       </c>
       <c r="I370" s="7" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.4">
@@ -6539,7 +6539,7 @@
         <v>335</v>
       </c>
       <c r="I371" s="7" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.4">
@@ -6547,7 +6547,7 @@
         <v>336</v>
       </c>
       <c r="I372" s="7" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.4">
@@ -6555,7 +6555,7 @@
         <v>337</v>
       </c>
       <c r="I373" s="7" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.4">
@@ -6563,7 +6563,7 @@
         <v>338</v>
       </c>
       <c r="I374" s="7" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.4">
@@ -6571,7 +6571,7 @@
         <v>339</v>
       </c>
       <c r="I375" s="7" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.4">
@@ -6579,7 +6579,7 @@
         <v>340</v>
       </c>
       <c r="I376" s="7" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.4">
@@ -6587,7 +6587,7 @@
         <v>341</v>
       </c>
       <c r="I377" s="7" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.4">
@@ -6595,7 +6595,7 @@
         <v>342</v>
       </c>
       <c r="I378" s="7" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.4">
@@ -6603,7 +6603,7 @@
         <v>343</v>
       </c>
       <c r="I379" s="7" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="380" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">

--- a/app/templates_excel/nigredo/n7_asteroids_en.xlsx
+++ b/app/templates_excel/nigredo/n7_asteroids_en.xlsx
@@ -1680,10 +1680,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A pagent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sunshine just after a storm.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2444,10 +2440,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A tree feiled and sawed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Butterfly emerging from a chrysalis.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2544,10 +2536,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>An inhibited island.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The purging of the priesthood.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2605,6 +2593,18 @@
   </si>
   <si>
     <t>A widow at an open grave.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A tree felled and sawed.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An inhabited island.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A pageant.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3593,7 +3593,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="6" t="s">
         <v>14</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" s="6" t="s">
         <v>15</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="6" t="s">
         <v>16</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
         <v>17</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" s="6" t="s">
         <v>18</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A29" s="6" t="s">
         <v>19</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A30" s="6" t="s">
         <v>20</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A31" s="6" t="s">
         <v>21</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A32" s="6" t="s">
         <v>22</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
         <v>23</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A34" s="6" t="s">
         <v>24</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A35" s="6" t="s">
         <v>25</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
         <v>26</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
         <v>27</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A38" s="6" t="s">
         <v>28</v>
       </c>
@@ -3713,30 +3713,30 @@
         <v>402</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A40" s="9" t="s">
         <v>363</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A41" s="9" t="s">
         <v>364</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A42" s="9" t="s">
         <v>29</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A43" s="9" t="s">
         <v>30</v>
       </c>
@@ -3768,15 +3768,15 @@
         <v>406</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A44" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A45" s="9" t="s">
         <v>32</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A46" s="9" t="s">
         <v>33</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A47" s="9" t="s">
         <v>34</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A48" s="9" t="s">
         <v>35</v>
       </c>
@@ -3808,15 +3808,15 @@
         <v>410</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A49" s="9" t="s">
         <v>36</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A50" s="9" t="s">
         <v>37</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A51" s="9" t="s">
         <v>38</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A52" s="9" t="s">
         <v>39</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A53" s="9" t="s">
         <v>40</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A54" s="9" t="s">
         <v>41</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A55" s="9" t="s">
         <v>42</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A56" s="9" t="s">
         <v>43</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A57" s="9" t="s">
         <v>44</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A58" s="9" t="s">
         <v>45</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A59" s="9" t="s">
         <v>46</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A60" s="9" t="s">
         <v>47</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A61" s="9" t="s">
         <v>48</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A62" s="9" t="s">
         <v>49</v>
       </c>
@@ -3978,25 +3978,25 @@
     </row>
     <row r="70" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B70" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.4">
@@ -4004,7 +4004,7 @@
         <v>365</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.4">
@@ -4241,25 +4241,25 @@
     </row>
     <row r="101" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B101" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.4">
@@ -4355,7 +4355,7 @@
         <v>95</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.4">
@@ -4504,25 +4504,25 @@
     </row>
     <row r="132" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.4">
@@ -4562,7 +4562,7 @@
         <v>117</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.4">
@@ -4642,7 +4642,7 @@
         <v>127</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>502</v>
+        <v>733</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.4">
@@ -4650,7 +4650,7 @@
         <v>128</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.4">
@@ -4658,7 +4658,7 @@
         <v>129</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.4">
@@ -4666,7 +4666,7 @@
         <v>130</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.4">
@@ -4674,7 +4674,7 @@
         <v>131</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.4">
@@ -4682,7 +4682,7 @@
         <v>132</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.4">
@@ -4690,7 +4690,7 @@
         <v>133</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.4">
@@ -4698,7 +4698,7 @@
         <v>134</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.4">
@@ -4706,7 +4706,7 @@
         <v>135</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.4">
@@ -4714,7 +4714,7 @@
         <v>136</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.4">
@@ -4722,7 +4722,7 @@
         <v>137</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.4">
@@ -4730,7 +4730,7 @@
         <v>138</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.4">
@@ -4738,7 +4738,7 @@
         <v>139</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.4">
@@ -4746,7 +4746,7 @@
         <v>140</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.4">
@@ -4754,7 +4754,7 @@
         <v>141</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.4">
@@ -4762,30 +4762,30 @@
         <v>142</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="163" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B163" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.4">
@@ -4793,7 +4793,7 @@
         <v>369</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.4">
@@ -4801,7 +4801,7 @@
         <v>370</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.4">
@@ -4809,7 +4809,7 @@
         <v>143</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.4">
@@ -4817,7 +4817,7 @@
         <v>144</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>145</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.4">
@@ -4833,7 +4833,7 @@
         <v>146</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.4">
@@ -4841,7 +4841,7 @@
         <v>147</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.4">
@@ -4849,7 +4849,7 @@
         <v>148</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.4">
@@ -4857,7 +4857,7 @@
         <v>149</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.4">
@@ -4865,7 +4865,7 @@
         <v>150</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.4">
@@ -4873,7 +4873,7 @@
         <v>151</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>152</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.4">
@@ -4889,7 +4889,7 @@
         <v>153</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.4">
@@ -4897,7 +4897,7 @@
         <v>154</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.4">
@@ -4905,7 +4905,7 @@
         <v>155</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.4">
@@ -4913,7 +4913,7 @@
         <v>156</v>
       </c>
       <c r="I179" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.4">
@@ -4921,7 +4921,7 @@
         <v>157</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.4">
@@ -4929,7 +4929,7 @@
         <v>158</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>159</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.4">
@@ -4945,7 +4945,7 @@
         <v>160</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.4">
@@ -4953,7 +4953,7 @@
         <v>161</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.4">
@@ -4961,7 +4961,7 @@
         <v>162</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.4">
@@ -4969,7 +4969,7 @@
         <v>163</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.4">
@@ -4977,7 +4977,7 @@
         <v>164</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.4">
@@ -4985,7 +4985,7 @@
         <v>165</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>166</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.4">
@@ -5001,7 +5001,7 @@
         <v>167</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.4">
@@ -5009,7 +5009,7 @@
         <v>168</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.4">
@@ -5017,7 +5017,7 @@
         <v>169</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.4">
@@ -5025,30 +5025,30 @@
         <v>170</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="194" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B194" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H194" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.4">
@@ -5056,7 +5056,7 @@
         <v>371</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.4">
@@ -5064,7 +5064,7 @@
         <v>171</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.4">
@@ -5072,7 +5072,7 @@
         <v>172</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.4">
@@ -5080,7 +5080,7 @@
         <v>173</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.4">
@@ -5088,7 +5088,7 @@
         <v>174</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.4">
@@ -5096,7 +5096,7 @@
         <v>175</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.4">
@@ -5104,7 +5104,7 @@
         <v>176</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.4">
@@ -5112,7 +5112,7 @@
         <v>177</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.4">
@@ -5120,7 +5120,7 @@
         <v>178</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.4">
@@ -5128,7 +5128,7 @@
         <v>179</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.4">
@@ -5136,7 +5136,7 @@
         <v>180</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.4">
@@ -5144,7 +5144,7 @@
         <v>181</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.4">
@@ -5152,7 +5152,7 @@
         <v>182</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.4">
@@ -5160,7 +5160,7 @@
         <v>183</v>
       </c>
       <c r="I208" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.4">
@@ -5168,7 +5168,7 @@
         <v>184</v>
       </c>
       <c r="I209" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.4">
@@ -5176,7 +5176,7 @@
         <v>185</v>
       </c>
       <c r="I210" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.4">
@@ -5184,7 +5184,7 @@
         <v>186</v>
       </c>
       <c r="I211" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.4">
@@ -5192,7 +5192,7 @@
         <v>187</v>
       </c>
       <c r="I212" s="7" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.4">
@@ -5200,7 +5200,7 @@
         <v>188</v>
       </c>
       <c r="I213" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.4">
@@ -5208,7 +5208,7 @@
         <v>189</v>
       </c>
       <c r="I214" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.4">
@@ -5216,7 +5216,7 @@
         <v>190</v>
       </c>
       <c r="I215" s="7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.4">
@@ -5224,7 +5224,7 @@
         <v>191</v>
       </c>
       <c r="I216" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.4">
@@ -5232,7 +5232,7 @@
         <v>192</v>
       </c>
       <c r="I217" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.4">
@@ -5240,7 +5240,7 @@
         <v>193</v>
       </c>
       <c r="I218" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.4">
@@ -5248,7 +5248,7 @@
         <v>194</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.4">
@@ -5256,7 +5256,7 @@
         <v>195</v>
       </c>
       <c r="I220" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.4">
@@ -5264,7 +5264,7 @@
         <v>196</v>
       </c>
       <c r="I221" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.4">
@@ -5272,7 +5272,7 @@
         <v>197</v>
       </c>
       <c r="I222" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.4">
@@ -5280,7 +5280,7 @@
         <v>198</v>
       </c>
       <c r="I223" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.4">
@@ -5288,30 +5288,30 @@
         <v>199</v>
       </c>
       <c r="I224" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="225" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B225" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E225" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F225" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G225" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.4">
@@ -5319,7 +5319,7 @@
         <v>372</v>
       </c>
       <c r="I226" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.4">
@@ -5327,7 +5327,7 @@
         <v>200</v>
       </c>
       <c r="I227" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.4">
@@ -5335,7 +5335,7 @@
         <v>201</v>
       </c>
       <c r="I228" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.4">
@@ -5343,7 +5343,7 @@
         <v>202</v>
       </c>
       <c r="I229" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.4">
@@ -5351,7 +5351,7 @@
         <v>203</v>
       </c>
       <c r="I230" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.4">
@@ -5359,7 +5359,7 @@
         <v>204</v>
       </c>
       <c r="I231" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.4">
@@ -5367,7 +5367,7 @@
         <v>205</v>
       </c>
       <c r="I232" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.4">
@@ -5375,7 +5375,7 @@
         <v>206</v>
       </c>
       <c r="I233" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.4">
@@ -5383,7 +5383,7 @@
         <v>207</v>
       </c>
       <c r="I234" s="7" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.4">
@@ -5391,7 +5391,7 @@
         <v>208</v>
       </c>
       <c r="I235" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.4">
@@ -5399,7 +5399,7 @@
         <v>209</v>
       </c>
       <c r="I236" s="7" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.4">
@@ -5407,7 +5407,7 @@
         <v>210</v>
       </c>
       <c r="I237" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.4">
@@ -5415,7 +5415,7 @@
         <v>211</v>
       </c>
       <c r="I238" s="7" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.4">
@@ -5423,7 +5423,7 @@
         <v>212</v>
       </c>
       <c r="I239" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.4">
@@ -5431,7 +5431,7 @@
         <v>213</v>
       </c>
       <c r="I240" s="7" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.4">
@@ -5439,7 +5439,7 @@
         <v>214</v>
       </c>
       <c r="I241" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.4">
@@ -5447,7 +5447,7 @@
         <v>215</v>
       </c>
       <c r="I242" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.4">
@@ -5455,7 +5455,7 @@
         <v>216</v>
       </c>
       <c r="I243" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.4">
@@ -5463,7 +5463,7 @@
         <v>217</v>
       </c>
       <c r="I244" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.4">
@@ -5471,7 +5471,7 @@
         <v>218</v>
       </c>
       <c r="I245" s="7" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.4">
@@ -5479,7 +5479,7 @@
         <v>219</v>
       </c>
       <c r="I246" s="7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.4">
@@ -5487,7 +5487,7 @@
         <v>220</v>
       </c>
       <c r="I247" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.4">
@@ -5495,7 +5495,7 @@
         <v>221</v>
       </c>
       <c r="I248" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.4">
@@ -5503,7 +5503,7 @@
         <v>222</v>
       </c>
       <c r="I249" s="7" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.4">
@@ -5511,7 +5511,7 @@
         <v>223</v>
       </c>
       <c r="I250" s="7" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.4">
@@ -5519,7 +5519,7 @@
         <v>224</v>
       </c>
       <c r="I251" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.4">
@@ -5527,7 +5527,7 @@
         <v>225</v>
       </c>
       <c r="I252" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.4">
@@ -5535,7 +5535,7 @@
         <v>226</v>
       </c>
       <c r="I253" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.4">
@@ -5543,7 +5543,7 @@
         <v>227</v>
       </c>
       <c r="I254" s="7" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.4">
@@ -5551,30 +5551,30 @@
         <v>228</v>
       </c>
       <c r="I255" s="7" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="256" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B256" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C256" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E256" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F256" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G256" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H256" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.4">
@@ -5582,7 +5582,7 @@
         <v>373</v>
       </c>
       <c r="I257" s="7" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.4">
@@ -5590,7 +5590,7 @@
         <v>229</v>
       </c>
       <c r="I258" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.4">
@@ -5598,7 +5598,7 @@
         <v>230</v>
       </c>
       <c r="I259" s="7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.4">
@@ -5606,7 +5606,7 @@
         <v>231</v>
       </c>
       <c r="I260" s="7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.4">
@@ -5614,7 +5614,7 @@
         <v>232</v>
       </c>
       <c r="I261" s="7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.4">
@@ -5622,7 +5622,7 @@
         <v>233</v>
       </c>
       <c r="I262" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.4">
@@ -5630,7 +5630,7 @@
         <v>234</v>
       </c>
       <c r="I263" s="7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.4">
@@ -5638,7 +5638,7 @@
         <v>235</v>
       </c>
       <c r="I264" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.4">
@@ -5646,7 +5646,7 @@
         <v>236</v>
       </c>
       <c r="I265" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.4">
@@ -5654,7 +5654,7 @@
         <v>0</v>
       </c>
       <c r="I266" s="7" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.4">
@@ -5662,7 +5662,7 @@
         <v>237</v>
       </c>
       <c r="I267" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.4">
@@ -5670,7 +5670,7 @@
         <v>238</v>
       </c>
       <c r="I268" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.4">
@@ -5678,7 +5678,7 @@
         <v>239</v>
       </c>
       <c r="I269" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.4">
@@ -5686,7 +5686,7 @@
         <v>240</v>
       </c>
       <c r="I270" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.4">
@@ -5694,7 +5694,7 @@
         <v>241</v>
       </c>
       <c r="I271" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.4">
@@ -5702,7 +5702,7 @@
         <v>242</v>
       </c>
       <c r="I272" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.4">
@@ -5710,7 +5710,7 @@
         <v>243</v>
       </c>
       <c r="I273" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.4">
@@ -5718,7 +5718,7 @@
         <v>244</v>
       </c>
       <c r="I274" s="7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.4">
@@ -5726,7 +5726,7 @@
         <v>245</v>
       </c>
       <c r="I275" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.4">
@@ -5734,7 +5734,7 @@
         <v>246</v>
       </c>
       <c r="I276" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.4">
@@ -5742,7 +5742,7 @@
         <v>247</v>
       </c>
       <c r="I277" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.4">
@@ -5750,7 +5750,7 @@
         <v>248</v>
       </c>
       <c r="I278" s="7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.4">
@@ -5758,7 +5758,7 @@
         <v>249</v>
       </c>
       <c r="I279" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.4">
@@ -5766,7 +5766,7 @@
         <v>250</v>
       </c>
       <c r="I280" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.4">
@@ -5774,7 +5774,7 @@
         <v>251</v>
       </c>
       <c r="I281" s="7" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.4">
@@ -5782,7 +5782,7 @@
         <v>252</v>
       </c>
       <c r="I282" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.4">
@@ -5790,7 +5790,7 @@
         <v>253</v>
       </c>
       <c r="I283" s="7" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.4">
@@ -5798,7 +5798,7 @@
         <v>254</v>
       </c>
       <c r="I284" s="7" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.4">
@@ -5806,7 +5806,7 @@
         <v>255</v>
       </c>
       <c r="I285" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.4">
@@ -5814,30 +5814,30 @@
         <v>256</v>
       </c>
       <c r="I286" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="287" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B287" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F287" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G287" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H287" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.4">
@@ -5845,7 +5845,7 @@
         <v>374</v>
       </c>
       <c r="I288" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.4">
@@ -5853,7 +5853,7 @@
         <v>257</v>
       </c>
       <c r="I289" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.4">
@@ -5861,7 +5861,7 @@
         <v>258</v>
       </c>
       <c r="I290" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.4">
@@ -5869,7 +5869,7 @@
         <v>259</v>
       </c>
       <c r="I291" s="7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.4">
@@ -5877,7 +5877,7 @@
         <v>260</v>
       </c>
       <c r="I292" s="7" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.4">
@@ -5885,7 +5885,7 @@
         <v>261</v>
       </c>
       <c r="I293" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.4">
@@ -5893,7 +5893,7 @@
         <v>262</v>
       </c>
       <c r="I294" s="7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.4">
@@ -5901,7 +5901,7 @@
         <v>263</v>
       </c>
       <c r="I295" s="7" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.4">
@@ -5909,7 +5909,7 @@
         <v>264</v>
       </c>
       <c r="I296" s="7" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.4">
@@ -5917,7 +5917,7 @@
         <v>265</v>
       </c>
       <c r="I297" s="7" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.4">
@@ -5925,7 +5925,7 @@
         <v>266</v>
       </c>
       <c r="I298" s="7" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.4">
@@ -5933,7 +5933,7 @@
         <v>267</v>
       </c>
       <c r="I299" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.4">
@@ -5941,7 +5941,7 @@
         <v>268</v>
       </c>
       <c r="I300" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.4">
@@ -5949,7 +5949,7 @@
         <v>269</v>
       </c>
       <c r="I301" s="7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.4">
@@ -5957,7 +5957,7 @@
         <v>270</v>
       </c>
       <c r="I302" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.4">
@@ -5965,7 +5965,7 @@
         <v>271</v>
       </c>
       <c r="I303" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.4">
@@ -5973,7 +5973,7 @@
         <v>272</v>
       </c>
       <c r="I304" s="7" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.4">
@@ -5981,7 +5981,7 @@
         <v>273</v>
       </c>
       <c r="I305" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.4">
@@ -5989,7 +5989,7 @@
         <v>274</v>
       </c>
       <c r="I306" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.4">
@@ -5997,7 +5997,7 @@
         <v>275</v>
       </c>
       <c r="I307" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.4">
@@ -6005,7 +6005,7 @@
         <v>276</v>
       </c>
       <c r="I308" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.4">
@@ -6013,7 +6013,7 @@
         <v>277</v>
       </c>
       <c r="I309" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.4">
@@ -6021,7 +6021,7 @@
         <v>278</v>
       </c>
       <c r="I310" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.4">
@@ -6029,7 +6029,7 @@
         <v>279</v>
       </c>
       <c r="I311" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.4">
@@ -6037,7 +6037,7 @@
         <v>280</v>
       </c>
       <c r="I312" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.4">
@@ -6045,7 +6045,7 @@
         <v>281</v>
       </c>
       <c r="I313" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.4">
@@ -6053,7 +6053,7 @@
         <v>282</v>
       </c>
       <c r="I314" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.4">
@@ -6061,7 +6061,7 @@
         <v>283</v>
       </c>
       <c r="I315" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.4">
@@ -6069,7 +6069,7 @@
         <v>284</v>
       </c>
       <c r="I316" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.4">
@@ -6077,30 +6077,30 @@
         <v>285</v>
       </c>
       <c r="I317" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="318" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B318" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C318" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D318" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E318" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F318" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G318" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H318" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.4">
@@ -6108,7 +6108,7 @@
         <v>375</v>
       </c>
       <c r="I319" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.4">
@@ -6116,7 +6116,7 @@
         <v>286</v>
       </c>
       <c r="I320" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.4">
@@ -6124,7 +6124,7 @@
         <v>287</v>
       </c>
       <c r="I321" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.4">
@@ -6132,7 +6132,7 @@
         <v>288</v>
       </c>
       <c r="I322" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.4">
@@ -6140,7 +6140,7 @@
         <v>289</v>
       </c>
       <c r="I323" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.4">
@@ -6148,7 +6148,7 @@
         <v>290</v>
       </c>
       <c r="I324" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.4">
@@ -6156,7 +6156,7 @@
         <v>291</v>
       </c>
       <c r="I325" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.4">
@@ -6164,7 +6164,7 @@
         <v>292</v>
       </c>
       <c r="I326" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.4">
@@ -6172,7 +6172,7 @@
         <v>293</v>
       </c>
       <c r="I327" s="7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.4">
@@ -6180,7 +6180,7 @@
         <v>294</v>
       </c>
       <c r="I328" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.4">
@@ -6188,7 +6188,7 @@
         <v>295</v>
       </c>
       <c r="I329" s="7" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.4">
@@ -6196,7 +6196,7 @@
         <v>296</v>
       </c>
       <c r="I330" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.4">
@@ -6204,7 +6204,7 @@
         <v>297</v>
       </c>
       <c r="I331" s="7" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.4">
@@ -6212,7 +6212,7 @@
         <v>298</v>
       </c>
       <c r="I332" s="7" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.4">
@@ -6220,7 +6220,7 @@
         <v>299</v>
       </c>
       <c r="I333" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.4">
@@ -6228,7 +6228,7 @@
         <v>300</v>
       </c>
       <c r="I334" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.4">
@@ -6236,7 +6236,7 @@
         <v>301</v>
       </c>
       <c r="I335" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.4">
@@ -6244,7 +6244,7 @@
         <v>302</v>
       </c>
       <c r="I336" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.4">
@@ -6252,7 +6252,7 @@
         <v>303</v>
       </c>
       <c r="I337" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.4">
@@ -6260,7 +6260,7 @@
         <v>304</v>
       </c>
       <c r="I338" s="7" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.4">
@@ -6268,7 +6268,7 @@
         <v>305</v>
       </c>
       <c r="I339" s="7" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.4">
@@ -6276,7 +6276,7 @@
         <v>306</v>
       </c>
       <c r="I340" s="7" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.4">
@@ -6284,7 +6284,7 @@
         <v>307</v>
       </c>
       <c r="I341" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.4">
@@ -6292,7 +6292,7 @@
         <v>308</v>
       </c>
       <c r="I342" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.4">
@@ -6300,7 +6300,7 @@
         <v>309</v>
       </c>
       <c r="I343" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.4">
@@ -6308,7 +6308,7 @@
         <v>310</v>
       </c>
       <c r="I344" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.4">
@@ -6316,7 +6316,7 @@
         <v>311</v>
       </c>
       <c r="I345" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.4">
@@ -6324,7 +6324,7 @@
         <v>312</v>
       </c>
       <c r="I346" s="7" t="s">
-        <v>693</v>
+        <v>731</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.4">
@@ -6332,7 +6332,7 @@
         <v>313</v>
       </c>
       <c r="I347" s="7" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.4">
@@ -6340,30 +6340,30 @@
         <v>314</v>
       </c>
       <c r="I348" s="7" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="349" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B349" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C349" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D349" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E349" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F349" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G349" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H349" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.4">
@@ -6371,7 +6371,7 @@
         <v>376</v>
       </c>
       <c r="I350" s="7" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.4">
@@ -6379,7 +6379,7 @@
         <v>315</v>
       </c>
       <c r="I351" s="7" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.4">
@@ -6387,7 +6387,7 @@
         <v>316</v>
       </c>
       <c r="I352" s="7" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.4">
@@ -6395,7 +6395,7 @@
         <v>317</v>
       </c>
       <c r="I353" s="7" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.4">
@@ -6403,7 +6403,7 @@
         <v>318</v>
       </c>
       <c r="I354" s="7" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.4">
@@ -6411,7 +6411,7 @@
         <v>319</v>
       </c>
       <c r="I355" s="7" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.4">
@@ -6419,7 +6419,7 @@
         <v>320</v>
       </c>
       <c r="I356" s="7" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.4">
@@ -6427,7 +6427,7 @@
         <v>321</v>
       </c>
       <c r="I357" s="7" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.4">
@@ -6435,7 +6435,7 @@
         <v>322</v>
       </c>
       <c r="I358" s="7" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.4">
@@ -6443,7 +6443,7 @@
         <v>323</v>
       </c>
       <c r="I359" s="7" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.4">
@@ -6451,7 +6451,7 @@
         <v>324</v>
       </c>
       <c r="I360" s="7" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.4">
@@ -6459,7 +6459,7 @@
         <v>325</v>
       </c>
       <c r="I361" s="7" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.4">
@@ -6467,7 +6467,7 @@
         <v>326</v>
       </c>
       <c r="I362" s="7" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.4">
@@ -6475,7 +6475,7 @@
         <v>327</v>
       </c>
       <c r="I363" s="7" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.4">
@@ -6483,7 +6483,7 @@
         <v>328</v>
       </c>
       <c r="I364" s="7" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.4">
@@ -6491,7 +6491,7 @@
         <v>329</v>
       </c>
       <c r="I365" s="7" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.4">
@@ -6499,7 +6499,7 @@
         <v>330</v>
       </c>
       <c r="I366" s="7" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.4">
@@ -6507,7 +6507,7 @@
         <v>331</v>
       </c>
       <c r="I367" s="7" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.4">
@@ -6515,7 +6515,7 @@
         <v>332</v>
       </c>
       <c r="I368" s="7" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.4">
@@ -6523,7 +6523,7 @@
         <v>333</v>
       </c>
       <c r="I369" s="7" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.4">
@@ -6531,7 +6531,7 @@
         <v>334</v>
       </c>
       <c r="I370" s="7" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.4">
@@ -6539,7 +6539,7 @@
         <v>335</v>
       </c>
       <c r="I371" s="7" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.4">
@@ -6547,7 +6547,7 @@
         <v>336</v>
       </c>
       <c r="I372" s="7" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.4">
@@ -6555,7 +6555,7 @@
         <v>337</v>
       </c>
       <c r="I373" s="7" t="s">
-        <v>718</v>
+        <v>732</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.4">
@@ -6563,7 +6563,7 @@
         <v>338</v>
       </c>
       <c r="I374" s="7" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.4">
@@ -6571,7 +6571,7 @@
         <v>339</v>
       </c>
       <c r="I375" s="7" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.4">
@@ -6579,7 +6579,7 @@
         <v>340</v>
       </c>
       <c r="I376" s="7" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.4">
@@ -6587,7 +6587,7 @@
         <v>341</v>
       </c>
       <c r="I377" s="7" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.4">
@@ -6595,7 +6595,7 @@
         <v>342</v>
       </c>
       <c r="I378" s="7" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.4">
@@ -6603,7 +6603,7 @@
         <v>343</v>
       </c>
       <c r="I379" s="7" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="380" spans="1:9" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
